--- a/plan/phase3/sonarqube-results.xlsx
+++ b/plan/phase3/sonarqube-results.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ellio\Documents\MCT\AJ2025-2026\bachelorproef\thesis_research\plan\phase3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BEBCB7F-28DB-4830-9DF9-7FF90266B7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A337E0-9E97-4309-BA77-5BF3B9B313E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{5E0614B8-F26E-4086-B04C-44636B2E8DE9}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{5E0614B8-F26E-4086-B04C-44636B2E8DE9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="timing" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="22">
   <si>
     <t>m3</t>
   </si>
@@ -82,11 +83,38 @@
   <si>
     <t>Intentionality</t>
   </si>
+  <si>
+    <t>methodology</t>
+  </si>
+  <si>
+    <t>stack</t>
+  </si>
+  <si>
+    <t>plan time</t>
+  </si>
+  <si>
+    <t>execution time</t>
+  </si>
+  <si>
+    <t>total time</t>
+  </si>
+  <si>
+    <t>avg</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="mm:ss.00"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -125,9 +153,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -914,7 +944,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3896-4F20-A7BB-C6714EA6D45B}"/>
+              <c16:uniqueId val="{00000000-BD9D-4F59-8295-29C00A1CA0D7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1025,7 +1055,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3896-4F20-A7BB-C6714EA6D45B}"/>
+              <c16:uniqueId val="{00000001-BD9D-4F59-8295-29C00A1CA0D7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1136,7 +1166,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3896-4F20-A7BB-C6714EA6D45B}"/>
+              <c16:uniqueId val="{00000002-BD9D-4F59-8295-29C00A1CA0D7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1343,6 +1373,464 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>timing!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>plan time</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>timing!$A$2:$B$7</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="6"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>nextjs</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>blazor</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>nextjs</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>blazor</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>nextjs</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>blazor</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>m1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>m1</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>m2</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>m2</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>m3</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>m3</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>timing!$C$2:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>mm:ss.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="2">
+                  <c:v>1.6984953703703704E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.073726851851852E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.1554398148148149E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5771990740740742E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9C7B-480E-92FC-4F908E981B55}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>timing!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>execution time</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>timing!$A$2:$B$7</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="6"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>nextjs</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>blazor</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>nextjs</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>blazor</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>nextjs</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>blazor</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>m1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>m1</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>m2</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>m2</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>m3</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>m3</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>timing!$D$2:$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>mm:ss.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>9.2644675925925932E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.8980324074074074E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.5541666666666665E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5890046296296296E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.2270833333333327E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.13587962962963E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9C7B-480E-92FC-4F908E981B55}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="548399168"/>
+        <c:axId val="160620944"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="548399168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="160620944"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="160620944"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="mm:ss.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="548399168"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1423,6 +1911,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
@@ -1929,6 +2457,511 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2475,23 +3508,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>201930</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>112395</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 7">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C28783A-836A-406A-A5E8-C9B3734491B5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37799556-FB97-489A-A4D2-261774B3B234}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2506,6 +3539,49 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00131648-6604-473F-BAA2-0F4C95AD4627}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3103,4 +4179,173 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{227BC10E-23ED-4F9C-BEFB-487E7738371E}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2">
+        <v>9.2644675925925932E-3</v>
+      </c>
+      <c r="E2" s="2">
+        <f>SUM(C2:D2)</f>
+        <v>9.2644675925925932E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2">
+        <v>6.8980324074074074E-3</v>
+      </c>
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E7" si="0">SUM(C3:D3)</f>
+        <v>6.8980324074074074E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1.6984953703703704E-3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>6.5541666666666665E-3</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" si="0"/>
+        <v>8.2526620370370375E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1.073726851851852E-3</v>
+      </c>
+      <c r="D5" s="2">
+        <v>6.5890046296296296E-3</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>7.6627314814814813E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2.1554398148148149E-3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>6.2270833333333327E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>8.3825231481481476E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1.5771990740740742E-3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4.13587962962963E-3</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
+        <v>5.7130787037037046E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2">
+        <f>AVERAGE(E2:E7)</f>
+        <v>7.695582561728395E-3</v>
+      </c>
+      <c r="F9" s="3">
+        <f>11.08</f>
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2">
+        <f>MIN(E2:E7)</f>
+        <v>5.7130787037037046E-3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2">
+        <f>MAX(E2:E7)</f>
+        <v>9.2644675925925932E-3</v>
+      </c>
+      <c r="F11" s="3">
+        <v>13.34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>